--- a/Financial Analysis/XYZ.xlsx
+++ b/Financial Analysis/XYZ.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BC3EE2-4A29-4B09-B8B2-B6F531BFAF2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B2BCB0-7352-4CE3-81E3-EB6EA583127B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{864B2951-E2B1-4041-AA94-9A7C8DF434B2}"/>
   </bookViews>
@@ -265,7 +265,7 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Slightly undervalued</t>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -788,14 +788,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>44.8</v>
+        <v>60.41</v>
       </c>
       <c r="E3" s="5">
-        <v>45779</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45782</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="5">
         <v>45870</v>
@@ -819,7 +819,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>27552</v>
+        <v>37152.15</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -861,7 +861,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>25571.599999999999</v>
+        <v>35171.75</v>
       </c>
     </row>
   </sheetData>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="AN41" s="2">
         <f>Main!D3</f>
-        <v>44.8</v>
+        <v>60.41</v>
       </c>
     </row>
     <row r="42" spans="2:40" x14ac:dyDescent="0.3">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AN42" s="10">
         <f>AN40/AN41-1</f>
-        <v>0.11667361343101468</v>
+        <v>-0.17187588343470517</v>
       </c>
     </row>
     <row r="43" spans="2:40" x14ac:dyDescent="0.3">

--- a/Financial Analysis/XYZ.xlsx
+++ b/Financial Analysis/XYZ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B2BCB0-7352-4CE3-81E3-EB6EA583127B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4A2894-21EE-441D-87FD-682C561B3579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{864B2951-E2B1-4041-AA94-9A7C8DF434B2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{864B2951-E2B1-4041-AA94-9A7C8DF434B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -788,14 +788,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>60.41</v>
+        <v>68.849999999999994</v>
       </c>
       <c r="E3" s="5">
-        <v>45804</v>
+        <v>45855</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45855</v>
       </c>
       <c r="G3" s="5">
         <v>45870</v>
@@ -819,7 +819,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>37152.15</v>
+        <v>42342.75</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -861,7 +861,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>35171.75</v>
+        <v>40362.35</v>
       </c>
     </row>
   </sheetData>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="AN41" s="2">
         <f>Main!D3</f>
-        <v>60.41</v>
+        <v>68.849999999999994</v>
       </c>
     </row>
     <row r="42" spans="2:40" x14ac:dyDescent="0.3">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AN42" s="10">
         <f>AN40/AN41-1</f>
-        <v>-0.17187588343470517</v>
+        <v>-0.27339175189964471</v>
       </c>
     </row>
     <row r="43" spans="2:40" x14ac:dyDescent="0.3">
